--- a/outputs/T-604_DEG色相_課題分離.xlsx
+++ b/outputs/T-604_DEG色相_課題分離.xlsx
@@ -7,11 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="課題の分離" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="事実と情報待ち" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="課題ツリー" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="背骨と情報待ち" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'課題の分離'!$3:$3</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'課題ツリー'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -36,14 +36,14 @@
     </font>
     <font>
       <name val="IPAGothic"/>
-      <color rgb="00404040"/>
-      <sz val="9"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="IPAGothic"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9.5"/>
+      <color rgb="00404040"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="IPAGothic"/>
@@ -54,12 +54,7 @@
     <font>
       <name val="IPAGothic"/>
       <color rgb="00000000"/>
-      <sz val="8.5"/>
-    </font>
-    <font>
-      <name val="IPAGothic"/>
-      <color rgb="00404040"/>
-      <sz val="8.5"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="IPAGothic"/>
@@ -69,11 +64,17 @@
     </font>
     <font>
       <name val="IPAGothic"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="IPAGothic"/>
       <color rgb="00000000"/>
       <sz val="9.5"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -88,6 +89,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EFEFEF"/>
       </patternFill>
     </fill>
     <fill>
@@ -141,35 +147,47 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -540,319 +558,298 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
     <col width="36" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>T-604 DEG色相悪化　イシュー特定と課題の分離（たたき台）</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="14" customHeight="1">
+          <t>T-604 DEG色相悪化　課題ツリー（たたき台・合意待ち草案）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="42" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>イシュー（草案）：T-604だけAPHAが上がり続けるのは、タンク固有の異常（内面の錆・付着が着色を促進）ではなく、むしろ貯めた液の履歴（NaOH停止後に初めて貯め始めた初期液が前駆体を多く含み、使い切られるまで鎖伸長が続いている）のせいなのでは。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="14" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
           <t>（2026-07-09 時点・たたき台）</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="3" t="n"/>
-      <c r="E2" s="3" t="n"/>
-      <c r="F2" s="3" t="n"/>
-    </row>
-    <row r="3" ht="44" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>分離軸
-（T-604と他タンクの
-違いの候補）</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>仮説
-（この違いがあればT-604だけの悪化を説明できる）</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>妥当と言えるための条件
-（何が確認できれば成り立つか）</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>既存整理での位置づけ</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>タンク開放所見との関係</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>確認に必要なデータ・分析</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="94.5" customHeight="1">
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+    </row>
+    <row r="4" ht="22" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>液の中身
-（受入・ブレンド）</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>悪化品（ポリエナール前駆体を含むDEG）の受入がT-604に集中し、前駆体濃度が最も高い液がここで長期滞留した。T-555・T-615にはブレンド・希釈後の液が回るため悪化が目立たない。</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>受払履歴で、悪化期間の初期流動品・悪化品の入槽先がT-604に偏っていたこと。T-555・T-615への移送がブレンド後だったこと。</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>既存メカニズム（450nm成長の場はタンク長滞留・前駆体が反応しきるとAPHA30前後で安定）と最も整合。初期タンク運用「T-604で受け、T-555・T-615へ展開しブレンドで調整」とも符合。</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>前駆体・重質物が最も多く通過・滞留したタンクなら、内面の付着・変色が最も強く出ることも同時に説明できる（付着は悪化の結果、という向きと同じ）。</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>タンク受払履歴（悪化期の受入元・量・ブレンド比率）。残液・付着物のUVチャートとGPC（T-555残液との比較）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="94.5" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>塩基性
-（Na・pH）</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>T-604内のNa濃度・pHが他タンクより高く、「A-ALDとNaの併存」の悪化条件がタンク内でも成立している。</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>T-604残液のNa・pHがT-555・T-615より有意に高いこと。Na投入管理履歴と品質の相関で、Na添加期の液がT-604に偏って入っていたこと。</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>主因の現行整理（A-ALD濃度上昇とNa存在の組み合わせ・7/1ほぼ合意）と直結。「Na停止でストリームは改善する一方、特定タンク(604)で濃度上昇事例あり」という既往記録とも符合。</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>塩基性そのものは内面の腐食・汚れを直接は説明しない（腐食は有機酸側の論点として分離）。</t>
-        </is>
-      </c>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>残液のpH・Na実測。Na投入・リン酸Na転換の時期とT-604受入時期の重なり。2008年比較はNa無添加期のため単純比較に限界がある点に留意。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="69.5" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>滞留時間
-・残液運用</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>T-604は回転が遅く残液が長く残る運用のため、鎖伸長（脱水縮合）の時間が他タンクより長い。</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>受払データから各タンクの平均滞留日数・残液量を出し、T-604が突出していること。</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>「450nm成長の場はタンク（長滞留）」と整合。本管DEGは27日でAPHA5以下・タンク品で450nmが成長する、という事実とも同じ向き。</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>長滞留であればスラッジ・付着の蓄積も説明しやすい。</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>タンク別の滞留日数・残液量の試算（受払履歴から）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="107" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>タンク内面の状態
-（腐食・付着物）</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>T-604内面の錆・付着物が着色の原因側（触媒または供給源）として働いている。</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>T-604付着物に、450nm成長へ直接つながる触媒作用または特異成分が確認されること。既往試験（鉄錆単独では着色しない・C-1503付着物はピーク380nmで実機450nmと別現象・黒色付着物混入でも450nmピーク再現せず）を覆す結果が必要。</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>既存整理では否定側が優勢（鉄サビは450nmの主因でない・サビは原因でなく結果の可能性＝前田）。ただし局所腐食・380nm寄与までは無罪と言い切っていない＝未確定を残す。</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>開放所見「状態が良くない」（詳細は情報待ち）を直接説明する仮説。ただし逆向きの説明（アルデヒド高濃度で生成した有機酸（ギ酸）がタンクを腐食させた＝悪化の結果）も既に立っており、原因か結果かの向き決めが本丸の論点。</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>付着物の元素・有機分析（Fe・P・Na・有機成分。T-555異物「ほぼ鉄」との比較）。付着物のDEG共存保管試験（450nm再現の有無）。肉厚測定と腐食部位の分布（液面部・底部・気相部のどこか）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="107" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>雰囲気
-（窒素シール・酸素）</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>T-604は酸素が特に入らず、悪化を止める側に働く酸素の効果が効いていない。または逆に微量のエアリークがあり、活性金属の生成に働いている（木村コメント＝活性金属の発生に微量酸素が必要）。</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>タンク別の窒素シール・呼吸・エアリークの実態に、T-604だけの差があること。</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>酸素雰囲気で悪化が止まる事実はあるが、T-555も窒素シールで残液はAPHA30で安定しており、雰囲気の差だけでは説明力が弱い。窒素抑制の機序自体が3説併存（ラジカル停止・CO2溶解pH低下・吸湿水分）で未確定。</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>エアリークや結露があれば、気相部の内面腐食と符合する。</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>シール窒素の設定・パージ量・酸素濃度の実測。腐食部位の分布との突き合わせ。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="57" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>水分・温度</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>T-604の液水分が特に低く鎖伸長が進みやすい。または温度が高く反応が速い。</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>タンク別の水分・温度実績に有意差があること。</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>水分の寄与度は感度2〜3割で未確定。温度はDEG色相への検証が弱いとして優先度を下げた経緯（木村判断・6/3）。</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>直接は説明しない。</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>タンク別の水分・温度データの比較（あれば）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="94.5" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>見え方
-（監視・運用の偏り）</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>タンク固有の差ではなく、悪化品の投入とUV450監視がT-604に集中しているため「T-604だけ悪化」に見えている。</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>同等の悪化品をT-555・T-615に入れた場合に同程度の速度（1日あたり0.004程度）でUV450が上昇すれば、タンク固有差は否定される。</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>T-604はUV450早期判定の実績タンク（4/13からのデータで悪化品投入時1日あたり約0.004上昇・正常品はベース0.002から動かない）＝監視が最も密なタンクであることは事実。</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>開放所見は説明しない（設備側の課題として分離）。</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>入槽先別のUV450推移の比較。製品ストリームのボンベサンプリング（色相悪化がプラント由来かタンク由来かの切り分け・向後提案）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="40" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>本表はたたき台。列の意味（特に「確認に必要なデータ・分析」が何に向けた確認か）と行の粒度は、木村さんの用途に合わせて調整する。具体データが入り次第、各行の「妥当と言えるための条件」を満たすか順に潰していく。</t>
-        </is>
-      </c>
-      <c r="B12" s="9" t="n"/>
-      <c r="C12" s="9" t="n"/>
-      <c r="D12" s="9" t="n"/>
-      <c r="E12" s="9" t="n"/>
-      <c r="F12" s="9" t="n"/>
+          <t>番号</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>課題（仮説）</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>検証方法</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>対応（検証が当たれば）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>T-604だけAPHAが上がり続けるのは、貯めた液の履歴のせいなのでは（タンク固有の異常ではなく）</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr"/>
+      <c r="D5" s="8" t="inlineStr"/>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>A-1</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>初期在庫（NaOH停止後からリン酸開始前）は前駆体を最も多く含む液だったのでは</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr"/>
+      <c r="D6" s="11" t="inlineStr"/>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>A-1-①</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>貯め始めの時期は悪化品期（3月末から4/20頃）に重なるはず</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>受払履歴で貯め始め日・受入元を確認</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>前駆体を含む液が残る間は仕分け・ブレンド前提の出荷運用</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>A-1-②</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>T-604残液はT-615残液より前駆体が多いはず</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>残液のUVチャート・GPCを両タンクで比較</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>残液の処理（抜き出し・希釈）を検討</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>A-2</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>リン酸添加品を後から入れてもAPHAが上がり続けたのは、タンク内で鎖伸長が続いているためなのでは</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr"/>
+      <c r="D9" s="11" t="inlineStr"/>
+    </row>
+    <row r="10" ht="44.5" customHeight="1">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>A-2-①</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>上昇は前駆体が使い切られるまで続き、その後APHA30前後で頭打ちになるはず</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>T-604のAPHA・UV450推移が飽和型か（T-555の5/18以降安定と同型か）を確認</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>頭打ちが確認できれば、在庫の作り直しでなく時間経過とブレンドで収束を待つ選択肢が立つ</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="44.5" customHeight="1">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>A-2-②</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>リン酸は上流の前駆体生成に効き、タンク内の反応には効かないのでは</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>T-615（低下）との上昇速度比較で切り分け</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>リン酸投入判断を「タンクを治す」でなく「前駆体を入れない」目的に整理し直す</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="44.5" customHeight="1">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>A-3</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>（反証側）同じ液を入れてもT-604だけ上がるなら、タンク固有差なのでは</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>同等液の入槽先別UV450比較。ボンベサンプリング（プラント由来かタンク由来かの切り分け）</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>タンク固有差ならB系（設備側）を色相対策に昇格</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>開放で内面の状態が良くないのは、着色の原因ではなくむしろ結果（初期液の有機酸による腐食）なのでは</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr"/>
+      <c r="D13" s="8" t="inlineStr"/>
+    </row>
+    <row r="14" ht="32" customHeight="1">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>B-1</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>NaOH停止で有機酸（ギ酸）の中和がなくなり、初期液が内面を腐食させたのでは</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>残液の有機酸・pH実測。腐食部位の分布（液相部か気相部か）の確認</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>腐食は液側の運用改善（前駆体・有機酸を入れない）で再発防止</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="57" customHeight="1">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>B-2</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>（反証側）付着物が450nm成長の触媒・供給源として働いているのでは</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>付着物の元素分析（Fe・P・Na）とDEG共存保管試験で450nm再現の有無（T-555異物「ほぼ鉄」と比較）</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>再現すればタンク清掃・内面処理を色相対策に昇格</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="32" customHeight="1">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>B-3</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>腐食の程度が使用継続に耐えるかは、色相と切り離した設備健全性の判断のはず</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>肉厚測定・開放検査結果の整理</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>補修・使用可否の判断（色相の結論を待たずに進める）</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -868,221 +865,219 @@
   <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="104" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="10" t="inlineStr">
-        <is>
-          <t>イシューの構図（2つに分離する）</t>
-        </is>
-      </c>
-      <c r="B1" s="9" t="n"/>
-    </row>
-    <row r="2" ht="52" customHeight="1">
-      <c r="A2" s="11" t="inlineStr">
-        <is>
-          <t>イシュー1
-（液の課題）</t>
-        </is>
-      </c>
-      <c r="B2" s="12" t="inlineStr">
-        <is>
-          <t>T-604だけDEG色相悪化が進むのはなぜか。主仮説は「何が入ったか（前駆体）」「何と一緒か（Na）」「どれだけ置いたか（滞留）」の組み合わせ＝タンクの個体差ではなく運用の差で説明する筋が、既存整理と最も整合する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="52" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>イシュー2
-（設備の課題）</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>T-604開放で内面の状態が良くないのはなぜか・健全性をどう回復するか。既存整理では「腐食・付着は悪化の結果（アルデヒド高濃度で生成した有機酸による腐食）」の可能性が高い側。色相の原因究明とは切り離し、設備健全性（肉厚・補修）として進める。</t>
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>背骨（事実・見極め・対応）</t>
+        </is>
+      </c>
+      <c r="B1" s="14" t="n"/>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="15" t="inlineStr">
+        <is>
+          <t>事実</t>
+        </is>
+      </c>
+      <c r="B2" s="16" t="inlineStr">
+        <is>
+          <t>T-604はNaOH停止後に初めて貯め始めたタンク（それまで在庫なし）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="37" customHeight="1">
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>事実</t>
+        </is>
+      </c>
+      <c r="B3" s="16" t="inlineStr">
+        <is>
+          <t>リン酸添加品を貯めてもT-604はAPHA上昇が継続。T-615はリン酸添加後に低下傾向＝この実測差が最大の特徴。</t>
         </is>
       </c>
     </row>
     <row r="4" ht="37" customHeight="1">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>両者の接続点</t>
-        </is>
-      </c>
-      <c r="B4" s="12" t="inlineStr">
-        <is>
-          <t>付着物分析だけが両イシューをつなぐ（付着・錆が色相悪化の原因か、悪化の結果かの向き決め）。ここを最初に確定させると課題が完全に分離できる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
-        <is>
-          <t>動かない事実（前提）</t>
-        </is>
-      </c>
-      <c r="B6" s="9" t="n"/>
-    </row>
-    <row r="7" ht="37" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>事実</t>
+        </is>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>T-604開放で内面の状態が良くない（所見の詳細は情報収集中）。T-555（6/16初回開放）は比較的綺麗・異物はほぼ鉄。T-615（6/17）もT-555と同程度。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="37" customHeight="1">
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>事実</t>
+        </is>
+      </c>
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>既存整理＝前駆体はタンク長滞留で鎖伸長し、使い切られるとAPHA30前後で安定（T-555残液実測）。鉄錆単独では着色しない（保管試験）。主要因はA-ALD濃度上昇とNa存在の組み合わせ（7/1ほぼ合意）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="26" customHeight="1">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>見極め</t>
+        </is>
+      </c>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>①T-604とT-615の残液で前駆体（UVチャート・GPC）に差があるか（A-1-②）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="26" customHeight="1">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>見極め</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>②付着物が450nm成長の触媒になるか＝錆・付着が原因か結果かの向き決め（B-2）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>見極め</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>③T-604のAPHA上昇が飽和型か上がり続けているか（A-2-①）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="37" customHeight="1">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>対応</t>
+        </is>
+      </c>
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>液の履歴が当たりなら運用側（前駆体を含む液の受入管理・仕分け・ブレンド・残液処理）。反証が当たりなら設備側（清掃・補修・使用可否）。どちらに転んでも次の打ち手が決まる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>情報待ち（入り次第ツリーに反映）</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="n"/>
+    </row>
+    <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B7" s="12" t="inlineStr">
-        <is>
-          <t>着色物質は共役ポリエナール類（基礎研GPCで実測・MW200〜800）。主因はA-ALD由来（F-ALD・G-ALDも一部寄与）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="37" customHeight="1">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>T-604開放所見の詳細（部位・色・付着量・腐食の程度・写真）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="26" customHeight="1">
+      <c r="A13" s="15" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B8" s="12" t="inlineStr">
-        <is>
-          <t>450nm成長の場はタンク（長滞留）。前駆体が反応しきるとAPHA30前後で安定（T-555・T-604残液と整合）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>タンク受払履歴（貯め始め日・受入元・悪化品期との重なり・ブレンド比率）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B9" s="12" t="inlineStr">
-        <is>
-          <t>酸素雰囲気（船・ローリー）では悪化が止まる。鉄錆単独では着色しない（保管試験の実測）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>残液・付着物の分析結果（UVチャート・GPC・pH・Na・Fe・P・有機酸）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="26" customHeight="1">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B10" s="12" t="inlineStr">
-        <is>
-          <t>運用で色相に効いたのはリン酸Na（Na3PO4）のみ。継続投入が前提（止めると戻る）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="37" customHeight="1">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B11" s="12" t="inlineStr">
-        <is>
-          <t>主要因は「A-ALD濃度上昇」と「Naの存在」の組み合わせでほぼ合意（7/1）。2008年にアセト高でも問題が出なかったのはNa無添加のため。</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="37" customHeight="1">
-      <c r="A12" s="11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B12" s="12" t="inlineStr">
-        <is>
-          <t>T-604のUV450実績＝悪化品投入時は1日あたり約0.004上昇・正常品はベース0.002から動かない（4/13以降）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="37" customHeight="1">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B13" s="12" t="inlineStr">
-        <is>
-          <t>T-555（6/16初回開放）は黒色異物少なく比較的綺麗・異物はほぼ鉄。T-615（6/17）もT-555と同程度。T-555残液は5/18以降APHA上昇なし。</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="11" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B14" s="12" t="inlineStr">
-        <is>
-          <t>今回のT-604開放では内面の状態が良くない（所見の詳細は情報収集中）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="10" t="inlineStr">
-        <is>
-          <t>情報待ち（入り次第この表に反映）</t>
-        </is>
-      </c>
-      <c r="B16" s="9" t="n"/>
-    </row>
-    <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="B15" s="16" t="inlineStr">
+        <is>
+          <t>T-604とT-615のAPHA・UV450推移の並記データ（リン酸添加品受入の前後）</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>合意待ちの点（この草案で確認すること）</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="n"/>
+    </row>
+    <row r="18" ht="26" customHeight="1">
+      <c r="A18" s="15" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B17" s="12" t="inlineStr">
-        <is>
-          <t>T-604開放所見の詳細（部位・色・付着量・腐食の程度・写真）</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="26" customHeight="1">
-      <c r="A18" s="11" t="inlineStr">
+      <c r="B18" s="16" t="inlineStr">
+        <is>
+          <t>イシュー1文の向き（「タンク固有ではなく液の履歴」という対置）でよいか</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B18" s="12" t="inlineStr">
-        <is>
-          <t>タンク受払履歴（悪化期の受入元・ブレンド比率・滞留日数）</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="26" customHeight="1">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="B19" s="16" t="inlineStr">
+        <is>
+          <t>「検証方法」列を何に向けた検証として書くか（原因究明用か、会議説明用か）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="26" customHeight="1">
+      <c r="A20" s="15" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B19" s="12" t="inlineStr">
-        <is>
-          <t>残液・付着物の分析結果（UVチャート・pH・Na・Fe・P）</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="26" customHeight="1">
-      <c r="A20" s="11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B20" s="12" t="inlineStr">
-        <is>
-          <t>窒素シール・酸素濃度の実態（タンク別）</t>
+      <c r="B20" s="16" t="inlineStr">
+        <is>
+          <t>A-2-①「頭打ちになるはず」は足元のT-604推移次第で書き方を変える（上がり続けているなら弱い主張）</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A11:B11"/>
     <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A17:B17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>

--- a/outputs/T-604_DEG色相_課題分離.xlsx
+++ b/outputs/T-604_DEG色相_課題分離.xlsx
@@ -558,7 +558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -574,10 +574,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="42" customHeight="1">
+    <row r="2" ht="57" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>イシュー（草案）：T-604だけAPHAが上がり続けるのは、タンク固有の異常（内面の錆・付着が着色を促進）ではなく、むしろ貯めた液の履歴（NaOH停止後に初めて貯め始めた初期液が前駆体を多く含み、使い切られるまで鎖伸長が続いている）のせいなのでは。</t>
+          <t>イシュー（草案）：色相悪化は全タンクで起きているが、T-604がNaOH停止後の液・リン酸添加品を受けてもAPHA5未満から30まで上がり続けた（T-615は低下傾向）のは、液の質だけでは説明できず、むしろT-604固有の条件（TEGからの品名変更で4月に開放復帰した内面状態・コーティング・3基中最小の500tゆえの壁面/底板影響）が悪化を加速しているのでは。</t>
         </is>
       </c>
     </row>
@@ -621,13 +621,13 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>T-604だけAPHAが上がり続けるのは、貯めた液の履歴のせいなのでは（タンク固有の異常ではなく）</t>
+          <t>T-604固有の条件（内面・コーティング・幾何）が、全タンク共通の悪化を加速しているのでは</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr"/>
       <c r="D5" s="8" t="inlineStr"/>
     </row>
-    <row r="6" ht="32" customHeight="1">
+    <row r="6" ht="44.5" customHeight="1">
       <c r="A6" s="9" t="inlineStr">
         <is>
           <t>A-1</t>
@@ -635,13 +635,13 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>初期在庫（NaOH停止後からリン酸開始前）は前駆体を最も多く含む液だったのでは</t>
+          <t>コーティング仕様の食い違い（本日会議発言＝元々FRP／4/1調査資料＝エポキシ）をまず決着させるべきはず</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr"/>
       <c r="D6" s="11" t="inlineStr"/>
     </row>
-    <row r="7" ht="32" customHeight="1">
+    <row r="7" ht="57" customHeight="1">
       <c r="A7" s="9" t="inlineStr">
         <is>
           <t>A-1-①</t>
@@ -649,21 +649,21 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>貯め始めの時期は悪化品期（3月末から4/20頃）に重なるはず</t>
+          <t>図面・塗装仕様書・補修履歴で仕様と補修歴を確定できるはず</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>受払履歴で貯め始め日・受入元を確認</t>
+          <t>操油課・機械Grに図面・塗装記録・膜厚データの確認を依頼（過去の補修履歴含む）</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>前駆体を含む液が残る間は仕分け・ブレンド前提の出荷運用</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="32" customHeight="1">
+          <t>FRPなら他タンクとの仕様差が主対象に。エポキシなら材質差仮説は落ちて内面状態（劣化・剥離）の議論に移る</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="44.5" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
         <is>
           <t>A-1-②</t>
@@ -671,21 +671,21 @@
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>T-604残液はT-615残液より前駆体が多いはず</t>
+          <t>FRPだった場合、DEG・有機酸への耐性がエポキシより弱く、劣化・溶出・剥離が「加速」の説明になるのでは</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>残液のUVチャート・GPCを両タンクで比較</t>
+          <t>剥離片・付着物の分析（樹脂成分の同定）。膜厚・剥離範囲の記録</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>残液の処理（抜き出し・希釈）を検討</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="32" customHeight="1">
+          <t>再コーティング仕様（エポキシ化・全面補修）を復旧計画に織り込む</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="44.5" customHeight="1">
       <c r="A9" s="9" t="inlineStr">
         <is>
           <t>A-2</t>
@@ -693,7 +693,7 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>リン酸添加品を後から入れてもAPHAが上がり続けたのは、タンク内で鎖伸長が続いているためなのでは</t>
+          <t>TEGからの品名変更（4月開放復帰）の影響＝TEG時代の残渣・付着や、開放時の清掃・点検の程度が効いたのでは</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr"/>
@@ -707,21 +707,21 @@
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>上昇は前駆体が使い切られるまで続き、その後APHA30前後で頭打ちになるはず</t>
+          <t>4月開放時の点検・清掃の記録と今回所見を照合すれば、当時からあったものか今回できたものか分かるはず</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>T-604のAPHA・UV450推移が飽和型か（T-555の5/18以降安定と同型か）を確認</t>
+          <t>4月開放時の点検記録との照合（機械Gr宿題・石塚さん論点＝前回復旧判断との整合）</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>頭打ちが確認できれば、在庫の作り直しでなく時間経過とブレンドで収束を待つ選択肢が立つ</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="44.5" customHeight="1">
+          <t>点検・復旧判断の基準を明文化し、今回の復旧判断に織り込む</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="69.5" customHeight="1">
       <c r="A11" s="9" t="inlineStr">
         <is>
           <t>A-2-②</t>
@@ -729,21 +729,21 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>リン酸は上流の前駆体生成に効き、タンク内の反応には効かないのでは</t>
+          <t>4月開放時に四隅から採取した残液と今回の残液・付着物に、タンク由来成分（Fe・コーティング成分・TEG由来）が出るはず</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>T-615（低下）との上昇速度比較で切り分け</t>
+          <t>四隅残液サンプルの分析（野田さん宿題・金枝さん受け渡し調整）。T-555（茶褐色汚れ）・T-615（鉄サビ・砂＋鉄10〜12%）の分析結果と比較</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>リン酸投入判断を「タンクを治す」でなく「前駆体を入れない」目的に整理し直す</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="44.5" customHeight="1">
+          <t>タンク由来成分が出れば清掃・内面処理を色相対策に昇格。出なければ液側（B系）が強まる</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="57" customHeight="1">
       <c r="A12" s="9" t="inlineStr">
         <is>
           <t>A-3</t>
@@ -751,97 +751,155 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>（反証側）同じ液を入れてもT-604だけ上がるなら、タンク固有差なのでは</t>
+          <t>3基中最小（T-604 500t・T-615 950kL・T-555 2,000kL）で壁面/液比・底板影響（デッド在庫約2t・底板とドレンノズル間25mm）が最も濃く出るのでは</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>同等液の入槽先別UV450比較。ボンベサンプリング（プラント由来かタンク由来かの切り分け）</t>
+          <t>APHA上昇速度を在庫量・接液面積で規格化してタンク間比較</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>タンク固有差ならB系（設備側）を色相対策に昇格</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
+          <t>規格化で差が消えるなら「タンク固有」でなく共通機構＋幾何の差。消えなければA-1/A-2の固有要因を追う</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="44.5" customHeight="1">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>A-4</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>底板の状態不良・「他タンクより加速」（石塚さん所感）はA-1〜A-3の帰結として説明できるはず</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>T-604開放検査記録（写真・堆積物性状・コーティング状態・肉厚）の共有依頼</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>劣化速度が速ければ補修範囲・再発防止（内面仕様・受入液の管理）を復旧計画に反映</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="32" customHeight="1">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>開放で内面の状態が良くないのは、着色の原因ではなくむしろ結果（初期液の有機酸による腐食）なのでは</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr"/>
-      <c r="D13" s="8" t="inlineStr"/>
-    </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>（対抗仮説）液側で説明できる余地＝Na停止後でも残留Na・高A-ALD分が入っていたのでは</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr"/>
+      <c r="D14" s="8" t="inlineStr"/>
+    </row>
+    <row r="15" ht="44.5" customHeight="1">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>B-1</t>
         </is>
       </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>NaOH停止で有機酸（ギ酸）の中和がなくなり、初期液が内面を腐食させたのでは</t>
-        </is>
-      </c>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>残液の有機酸・pH実測。腐食部位の分布（液相部か気相部か）の確認</t>
-        </is>
-      </c>
-      <c r="D14" s="11" t="inlineStr">
-        <is>
-          <t>腐食は液側の運用改善（前駆体・有機酸を入れない）で再発防止</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="57" customHeight="1">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>塔内Na濃度は「低下傾向」であってゼロではなく、4/10〜4/20受入分はリン酸開始前で A-ALDも高かったはず</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>4月受入分の品質実績（Na・pH・A-ALD）確認。DEG色相UVデータ整形版の並記</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>液側で説明が付くなら、S/U後の受入管理（前駆体を含む液の仕分け）で対応</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="44.5" customHeight="1">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>B-2</t>
         </is>
       </c>
-      <c r="B15" s="10" t="inlineStr">
-        <is>
-          <t>（反証側）付着物が450nm成長の触媒・供給源として働いているのでは</t>
-        </is>
-      </c>
-      <c r="C15" s="11" t="inlineStr">
-        <is>
-          <t>付着物の元素分析（Fe・P・Na）とDEG共存保管試験で450nm再現の有無（T-555異物「ほぼ鉄」と比較）</t>
-        </is>
-      </c>
-      <c r="D15" s="11" t="inlineStr">
-        <is>
-          <t>再現すればタンク清掃・内面処理を色相対策に昇格</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="32" customHeight="1">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>B-3</t>
-        </is>
-      </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>腐食の程度が使用継続に耐えるかは、色相と切り離した設備健全性の判断のはず</t>
+          <t>全タンク悪化（5/11整理「タンク固有の可能性低い」）とT-604の速度差は、共通機構＋タンク条件の重ね合わせで説明できるはず</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>肉厚測定・開放検査結果の整理</t>
+          <t>タンク別のAPHA・UV450上昇速度の横並び比較（リン酸添加品受入の前後で区切る）</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>補修・使用可否の判断（色相の結論を待たずに進める）</t>
+          <t>共通機構側の対策（前駆体を入れない）とタンク側の対策（清掃・内面）の効き分けを整理</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="32" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>復旧判断（27日頃見込み）までに、色相と切り離して決めるべき設備側の判断があるはず</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr"/>
+      <c r="D17" s="8" t="inlineStr"/>
+    </row>
+    <row r="18" ht="44.5" customHeight="1">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>C-1</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>前回（4月）復旧判断との整合＝「前回ちゃんと点検できていないで復旧した」と言われない整理が要るはず</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>4月開放時の記録確認（機械Gr宿題）</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>点検・復旧の判断基準を記録に残す</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="44.5" customHeight="1">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>C-2</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>復帰後のT-604の使い方（端切り・共洗いの受け皿とするか＝6/22相談事項）は、原因の向きが決まってから決めるべきはず</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>A系・B系の見極め結果を待って判断材料を揃える</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>受け皿とする場合は悪化品の隔離運用、しない場合はS/U共洗い計画の見直し</t>
         </is>
       </c>
     </row>
@@ -862,7 +920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -877,7 +935,7 @@
       </c>
       <c r="B1" s="14" t="n"/>
     </row>
-    <row r="2" ht="26" customHeight="1">
+    <row r="2" ht="37" customHeight="1">
       <c r="A2" s="15" t="inlineStr">
         <is>
           <t>事実</t>
@@ -885,7 +943,7 @@
       </c>
       <c r="B2" s="16" t="inlineStr">
         <is>
-          <t>T-604はNaOH停止後に初めて貯め始めたタンク（それまで在庫なし）。</t>
+          <t>T-604はTEGタンクとして運用後（2025年12月〜2026年4月中旬）、品名変更（TEG→DEG）のため3〜4月に開放し、4/10からDEG受入を開始（色相5未満）。</t>
         </is>
       </c>
     </row>
@@ -897,11 +955,11 @@
       </c>
       <c r="B3" s="16" t="inlineStr">
         <is>
-          <t>リン酸添加品を貯めてもT-604はAPHA上昇が継続。T-615はリン酸添加後に低下傾向＝この実測差が最大の特徴。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="37" customHeight="1">
+          <t>受入品はNaOH停止（3/30）後の生産DEGが主で、4/20からはリン酸添加品。それでもAPHAは4/20の5未満から5/6に15（規格超過）、5/13に20、5/18に30まで悪化（実測）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="52" customHeight="1">
       <c r="A4" s="15" t="inlineStr">
         <is>
           <t>事実</t>
@@ -909,7 +967,7 @@
       </c>
       <c r="B4" s="16" t="inlineStr">
         <is>
-          <t>T-604開放で内面の状態が良くない（所見の詳細は情報収集中）。T-555（6/16初回開放）は比較的綺麗・異物はほぼ鉄。T-615（6/17）もT-555と同程度。</t>
+          <t>色相悪化は全タンクで発生（5/11調査の整理＝「タンク固有の不具合の可能性は低い」）。ストリーム品は常に規格内で、タンク（N2封入）保管中にのみ上昇。T-615はリン酸添加後に低下傾向、T-604は上昇継続＝速度差が特徴。</t>
         </is>
       </c>
     </row>
@@ -921,163 +979,235 @@
       </c>
       <c r="B5" s="16" t="inlineStr">
         <is>
-          <t>既存整理＝前駆体はタンク長滞留で鎖伸長し、使い切られるとAPHA30前後で安定（T-555残液実測）。鉄錆単独では着色しない（保管試験）。主要因はA-ALD濃度上昇とNa存在の組み合わせ（7/1ほぼ合意）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="26" customHeight="1">
+          <t>7/9開放（7/6〜清掃着手）でT-555・T-615と比較して状態が良くない・底板の状態が良くない・タッチアップ箇所が想定より多そう（金枝・木村）。所見詳細の記録は未入手。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="52" customHeight="1">
       <c r="A6" s="15" t="inlineStr">
         <is>
+          <t>事実（食い違い）</t>
+        </is>
+      </c>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>コーティング仕様＝本日会議発言では「T-604は元々FRP・タッチアップはエポキシ・T-555/T-615はエポキシ仕様」。一方4/1調査資料では「T-604内壁＝エポキシ樹脂コーティング（耐薬品性、実績あり）」。要決着。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="52" customHeight="1">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>事実</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>3基構成＝T-555 2,000kL・T-615 950kL・T-604 500t（最小）。T-604のデッド在庫約2t（底板とドレンノズル間25mm）。N2シール・シールポット・サンプリング装置は5/11時点で異常なし。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="37" customHeight="1">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>既存整理</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>着色物質はポリエナール（GPC実測）。鉄錆単独では着色しない（保管試験）。前駆体はタンク長滞留で鎖伸長し、使い切られるとAPHA30前後で安定（T-555残液実測）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
           <t>見極め</t>
         </is>
       </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>①T-604とT-615の残液で前駆体（UVチャート・GPC）に差があるか（A-1-②）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>①コーティング仕様の決着（図面・塗装記録・補修履歴）＝A-1。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="26" customHeight="1">
+      <c r="A10" s="15" t="inlineStr">
         <is>
           <t>見極め</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>②付着物が450nm成長の触媒になるか＝錆・付着が原因か結果かの向き決め（B-2）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>②4月開放時の点検・清掃記録と今回所見の照合（前回復旧判断の整合）＝A-2-①。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="37" customHeight="1">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>見極め</t>
         </is>
       </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>③T-604のAPHA上昇が飽和型か上がり続けているか（A-2-①）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="37" customHeight="1">
-      <c r="A9" s="15" t="inlineStr">
-        <is>
-          <t>対応</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>液の履歴が当たりなら運用側（前駆体を含む液の受入管理・仕分け・ブレンド・残液処理）。反証が当たりなら設備側（清掃・補修・使用可否）。どちらに転んでも次の打ち手が決まる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="13" t="inlineStr">
-        <is>
-          <t>情報待ち（入り次第ツリーに反映）</t>
-        </is>
-      </c>
-      <c r="B11" s="14" t="n"/>
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>③残液・付着物分析（四隅サンプル含む）でタンク由来成分（Fe・コーティング成分・TEG由来）が出るか＝A-2-②。</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="26" customHeight="1">
       <c r="A12" s="15" t="inlineStr">
         <is>
+          <t>見極め</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>④上昇速度を在庫量・接液面積で規格化した横並び比較＝A-3・B-2。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="37" customHeight="1">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>対応</t>
+        </is>
+      </c>
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>タンク側が当たりなら清掃・再コーティング仕様と復帰後の使い方（共洗い受け皿の是非）を決める。液側の余地（残留Na・4/10〜4/20の高A-ALD分）はB系で並行確認。どちらに転んでも次の打ち手が決まる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>情報待ち（入り次第ツリーに反映）</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="n"/>
+    </row>
+    <row r="16" ht="26" customHeight="1">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>T-604開放所見の詳細（部位・色・付着量・腐食の程度・写真）</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>本日（7/9）会議議事録＝開放所見の詳細（底板・側板・コーティングの状態、汚れ・錆の性状・範囲）</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="26" customHeight="1">
+      <c r="A17" s="15" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>タンク受払履歴（貯め始め日・受入元・悪化品期との重なり・ブレンド比率）</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>残液・付着物の分析結果（UVチャート・GPC・pH・Na・Fe・P・有機酸）</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>T-604とT-615のAPHA・UV450推移の並記データ（リン酸添加品受入の前後）</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="13" t="inlineStr">
-        <is>
-          <t>合意待ちの点（この草案で確認すること）</t>
-        </is>
-      </c>
-      <c r="B17" s="14" t="n"/>
+      <c r="B17" s="16" t="inlineStr">
+        <is>
+          <t>T-604開放検査記録（写真・堆積物性状・コーティング状態・肉厚測定）</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="26" customHeight="1">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B18" s="16" t="inlineStr">
         <is>
-          <t>イシュー1文の向き（「タンク固有ではなく液の履歴」という対置）でよいか</t>
+          <t>コーティング仕様の確定資料（図面・塗装仕様書・補修履歴・膜厚）</t>
         </is>
       </c>
     </row>
     <row r="19" ht="26" customHeight="1">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B19" s="16" t="inlineStr">
         <is>
-          <t>「検証方法」列を何に向けた検証として書くか（原因究明用か、会議説明用か）</t>
+          <t>4月開放時の点検記録（機械Gr宿題）</t>
         </is>
       </c>
     </row>
     <row r="20" ht="26" customHeight="1">
       <c r="A20" s="15" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B20" s="16" t="inlineStr">
+        <is>
+          <t>四隅残液サンプルの分析結果（野田さん宿題）</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="26" customHeight="1">
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B21" s="16" t="inlineStr">
+        <is>
+          <t>タンク別APHA・UV450上昇速度の横並びデータ（在庫量・接液面積での規格化用）</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>合意待ちの点（この草案で確認すること）</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="n"/>
+    </row>
+    <row r="24" ht="37" customHeight="1">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B24" s="16" t="inlineStr">
+        <is>
+          <t>イシューを「全タンク悪化の中でのT-604の速度差＝タンク固有条件の重ね合わせ」と設定し直した向きでよいか</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="37" customHeight="1">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B25" s="16" t="inlineStr">
+        <is>
+          <t>コーティング仕様の食い違い（会議発言FRP／4/1資料エポキシ）の決着を誰に確認するか（操油課図面か機械Grか）</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="26" customHeight="1">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>A-2-①「頭打ちになるはず」は足元のT-604推移次第で書き方を変える（上がり続けているなら弱い主張）</t>
+      <c r="B26" s="16" t="inlineStr">
+        <is>
+          <t>「検証方法」列を何に向けた検証として書くか（原因究明用か、会議説明用か）</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A15:B15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>

--- a/outputs/T-604_DEG色相_課題分離.xlsx
+++ b/outputs/T-604_DEG色相_課題分離.xlsx
@@ -558,7 +558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -574,10 +574,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="57" customHeight="1">
+    <row r="2" ht="72" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>イシュー（草案）：色相悪化は全タンクで起きているが、T-604がNaOH停止後の液・リン酸添加品を受けてもAPHA5未満から30まで上がり続けた（T-615は低下傾向）のは、液の質だけでは説明できず、むしろT-604固有の条件（TEGからの品名変更で4月に開放復帰した内面状態・コーティング・3基中最小の500tゆえの壁面/底板影響）が悪化を加速しているのでは。</t>
+          <t>イシュー（草案）：色相悪化は全タンクで起きているが、T-604がNaOH停止後の液・リン酸添加品を受けてもAPHA5未満から30まで上がり続けた（T-615は低下傾向）のは、液の質だけでは説明できず、むしろT-604固有の条件（元々FRPコーティングの内面とその劣化・TEGからの品名変更で4月に開放復帰した経緯・3基中最小の500tゆえの壁面/底板影響）が悪化を加速しているのでは。</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       <c r="C5" s="8" t="inlineStr"/>
       <c r="D5" s="8" t="inlineStr"/>
     </row>
-    <row r="6" ht="44.5" customHeight="1">
+    <row r="6" ht="57" customHeight="1">
       <c r="A6" s="9" t="inlineStr">
         <is>
           <t>A-1</t>
@@ -635,7 +635,7 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>コーティング仕様の食い違い（本日会議発言＝元々FRP／4/1調査資料＝エポキシ）をまず決着させるべきはず</t>
+          <t>コーティング材質の違い（T-604＝元々FRP・タッチアップはエポキシ／T-555・T-615＝エポキシ仕様。7/9平尾確認で会議内容が正と確定）が効いているのでは</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr"/>
@@ -649,21 +649,21 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>図面・塗装仕様書・補修履歴で仕様と補修歴を確定できるはず</t>
+          <t>FRP（不飽和ポリエステル系）はDEG・有機酸への耐性がエポキシより劣り、その劣化・剥離が「底板の状態不良」「タッチアップ箇所が想定より多い」「他タンクより加速」の説明になるのでは</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>操油課・機械Grに図面・塗装記録・膜厚データの確認を依頼（過去の補修履歴含む）</t>
+          <t>T-604開放検査記録（剥離範囲・膜厚・底板状態・タッチアップ箇所数）の共有依頼。FRPの樹脂系・積層仕様と補修履歴の確認（機械Gr）</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>FRPなら他タンクとの仕様差が主対象に。エポキシなら材質差仮説は落ちて内面状態（劣化・剥離）の議論に移る</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="44.5" customHeight="1">
+          <t>劣化が確認されれば再コーティング仕様（エポキシ化・全面補修）を復旧計画に織り込む</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="94.5" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
         <is>
           <t>A-1-②</t>
@@ -671,17 +671,17 @@
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>FRPだった場合、DEG・有機酸への耐性がエポキシより弱く、劣化・溶出・剥離が「加速」の説明になるのでは</t>
+          <t>FRP劣化が色相側にも効いているのでは（溶出成分のUV上乗せ・剥離部の裸鉄・粗面が前駆体を保持するリザーバ）</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>剥離片・付着物の分析（樹脂成分の同定）。膜厚・剥離範囲の記録</t>
+          <t>残液・四隅サンプル（4月採取・野田さん分析、金枝さん受け渡し調整）・付着物の分析で、タンク由来成分（FRP樹脂由来・Fe・TEG由来）を確認し、T-555（茶褐色汚れ）・T-615（鉄サビ・砂＋鉄10〜12%）と比較</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>再コーティング仕様（エポキシ化・全面補修）を復旧計画に織り込む</t>
+          <t>タンク由来成分が出れば清掃・内面処理を色相対策に昇格。出なければ液側（B系）が強まる</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>4月開放時の点検・清掃の記録と今回所見を照合すれば、当時からあったものか今回できたものか分かるはず</t>
+          <t>4月開放時の点検・清掃の記録と今回所見を照合すれば、劣化が当時からあったものか、この3か月でできたものか分かるはず</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
@@ -721,183 +721,161 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="69.5" customHeight="1">
+    <row r="11" ht="57" customHeight="1">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>A-2-②</t>
-        </is>
-      </c>
-      <c r="B11" s="12" t="inlineStr">
-        <is>
-          <t>4月開放時に四隅から採取した残液と今回の残液・付着物に、タンク由来成分（Fe・コーティング成分・TEG由来）が出るはず</t>
+          <t>A-3</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>3基中最小（T-604 500t・T-615 950kL・T-555 2,000kL）で壁面/液比・底板影響（デッド在庫約2t・底板とドレンノズル間25mm）が最も濃く出るのでは</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>四隅残液サンプルの分析（野田さん宿題・金枝さん受け渡し調整）。T-555（茶褐色汚れ）・T-615（鉄サビ・砂＋鉄10〜12%）の分析結果と比較</t>
+          <t>APHA上昇速度を在庫量・接液面積で規格化してタンク間比較</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>タンク由来成分が出れば清掃・内面処理を色相対策に昇格。出なければ液側（B系）が強まる</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="57" customHeight="1">
+          <t>規格化で差が消えるなら「タンク固有」でなく共通機構＋幾何の差。消えなければA-1/A-2の固有要因を追う</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="44.5" customHeight="1">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>A-3</t>
+          <t>A-4</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>3基中最小（T-604 500t・T-615 950kL・T-555 2,000kL）で壁面/液比・底板影響（デッド在庫約2t・底板とドレンノズル間25mm）が最も濃く出るのでは</t>
+          <t>底板の状態不良・「他タンクより加速」（石塚さん所感）はA-1〜A-3の帰結として説明できるはず</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>APHA上昇速度を在庫量・接液面積で規格化してタンク間比較</t>
+          <t>T-604開放検査記録（写真・堆積物性状・コーティング状態・肉厚）の共有依頼</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>規格化で差が消えるなら「タンク固有」でなく共通機構＋幾何の差。消えなければA-1/A-2の固有要因を追う</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="44.5" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>A-4</t>
-        </is>
-      </c>
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>底板の状態不良・「他タンクより加速」（石塚さん所感）はA-1〜A-3の帰結として説明できるはず</t>
-        </is>
-      </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>T-604開放検査記録（写真・堆積物性状・コーティング状態・肉厚）の共有依頼</t>
-        </is>
-      </c>
-      <c r="D13" s="11" t="inlineStr">
-        <is>
           <t>劣化速度が速ければ補修範囲・再発防止（内面仕様・受入液の管理）を復旧計画に反映</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="13" ht="32" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>（対抗仮説）液側で説明できる余地＝Na停止後でも残留Na・高A-ALD分が入っていたのでは</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr"/>
-      <c r="D14" s="8" t="inlineStr"/>
+      <c r="C13" s="8" t="inlineStr"/>
+      <c r="D13" s="8" t="inlineStr"/>
+    </row>
+    <row r="14" ht="44.5" customHeight="1">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>B-1</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>塔内Na濃度は「低下傾向」であってゼロではなく、4/10〜4/20受入分はリン酸開始前で A-ALDも高かったはず</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>4月受入分の品質実績（Na・pH・A-ALD）確認。DEG色相UVデータ整形版の並記</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>液側で説明が付くなら、S/U後の受入管理（前駆体を含む液の仕分け）で対応</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="44.5" customHeight="1">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>B-1</t>
+          <t>B-2</t>
         </is>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>塔内Na濃度は「低下傾向」であってゼロではなく、4/10〜4/20受入分はリン酸開始前で A-ALDも高かったはず</t>
+          <t>全タンク悪化（5/11整理「タンク固有の可能性低い」）とT-604の速度差は、共通機構＋タンク条件の重ね合わせで説明できるはず</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>4月受入分の品質実績（Na・pH・A-ALD）確認。DEG色相UVデータ整形版の並記</t>
+          <t>タンク別のAPHA・UV450上昇速度の横並び比較（リン酸添加品受入の前後で区切る）</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>液側で説明が付くなら、S/U後の受入管理（前駆体を含む液の仕分け）で対応</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="44.5" customHeight="1">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>B-2</t>
-        </is>
-      </c>
-      <c r="B16" s="10" t="inlineStr">
-        <is>
-          <t>全タンク悪化（5/11整理「タンク固有の可能性低い」）とT-604の速度差は、共通機構＋タンク条件の重ね合わせで説明できるはず</t>
-        </is>
-      </c>
-      <c r="C16" s="11" t="inlineStr">
-        <is>
-          <t>タンク別のAPHA・UV450上昇速度の横並び比較（リン酸添加品受入の前後で区切る）</t>
-        </is>
-      </c>
-      <c r="D16" s="11" t="inlineStr">
-        <is>
           <t>共通機構側の対策（前駆体を入れない）とタンク側の対策（清掃・内面）の効き分けを整理</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="32" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
+    <row r="16" ht="32" customHeight="1">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>復旧判断（27日頃見込み）までに、色相と切り離して決めるべき設備側の判断があるはず</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr"/>
-      <c r="D17" s="8" t="inlineStr"/>
+      <c r="C16" s="8" t="inlineStr"/>
+      <c r="D16" s="8" t="inlineStr"/>
+    </row>
+    <row r="17" ht="44.5" customHeight="1">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>C-1</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>前回（4月）復旧判断との整合＝「前回ちゃんと点検できていないで復旧した」と言われない整理が要るはず</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>4月開放時の記録確認（機械Gr宿題）</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>点検・復旧の判断基準を記録に残す</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="44.5" customHeight="1">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>C-1</t>
+          <t>C-2</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>前回（4月）復旧判断との整合＝「前回ちゃんと点検できていないで復旧した」と言われない整理が要るはず</t>
+          <t>復帰後のT-604の使い方（端切り・共洗いの受け皿とするか＝6/22相談事項）は、原因の向きが決まってから決めるべきはず</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>4月開放時の記録確認（機械Gr宿題）</t>
+          <t>A系・B系の見極め結果を待って判断材料を揃える</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
-        <is>
-          <t>点検・復旧の判断基準を記録に残す</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="44.5" customHeight="1">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>C-2</t>
-        </is>
-      </c>
-      <c r="B19" s="10" t="inlineStr">
-        <is>
-          <t>復帰後のT-604の使い方（端切り・共洗いの受け皿とするか＝6/22相談事項）は、原因の向きが決まってから決めるべきはず</t>
-        </is>
-      </c>
-      <c r="C19" s="11" t="inlineStr">
-        <is>
-          <t>A系・B系の見極め結果を待って判断材料を揃える</t>
-        </is>
-      </c>
-      <c r="D19" s="11" t="inlineStr">
         <is>
           <t>受け皿とする場合は悪化品の隔離運用、しない場合はS/U共洗い計画の見直し</t>
         </is>
@@ -986,12 +964,12 @@
     <row r="6" ht="52" customHeight="1">
       <c r="A6" s="15" t="inlineStr">
         <is>
-          <t>事実（食い違い）</t>
+          <t>事実（確定）</t>
         </is>
       </c>
       <c r="B6" s="16" t="inlineStr">
         <is>
-          <t>コーティング仕様＝本日会議発言では「T-604は元々FRP・タッチアップはエポキシ・T-555/T-615はエポキシ仕様」。一方4/1調査資料では「T-604内壁＝エポキシ樹脂コーティング（耐薬品性、実績あり）」。要決着。</t>
+          <t>コーティング仕様＝T-604は元々FRPコーティング・タッチアップはエポキシ・T-555/T-615はエポキシ仕様（7/9会議。平尾確認で会議内容が正と確定）。4/1調査資料の「T-604内壁＝エポキシ」記載は誤り＝訂正要。</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1005,7 @@
       </c>
       <c r="B9" s="16" t="inlineStr">
         <is>
-          <t>①コーティング仕様の決着（図面・塗装記録・補修履歴）＝A-1。</t>
+          <t>①FRP劣化の実態（剥離範囲・膜厚・補修履歴）と設備所見の対応＝A-1-①。</t>
         </is>
       </c>
     </row>
@@ -1051,7 +1029,7 @@
       </c>
       <c r="B11" s="16" t="inlineStr">
         <is>
-          <t>③残液・付着物分析（四隅サンプル含む）でタンク由来成分（Fe・コーティング成分・TEG由来）が出るか＝A-2-②。</t>
+          <t>③残液・付着物分析（四隅サンプル含む）でタンク由来成分（FRP樹脂由来・Fe・TEG由来）が出るか＝A-1-②。</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1085,7 @@
       </c>
       <c r="B17" s="16" t="inlineStr">
         <is>
-          <t>T-604開放検査記録（写真・堆積物性状・コーティング状態・肉厚測定）</t>
+          <t>T-604開放検査記録（写真・堆積物性状・コーティング状態・肉厚測定・タッチアップ箇所数）</t>
         </is>
       </c>
     </row>
@@ -1119,7 +1097,7 @@
       </c>
       <c r="B18" s="16" t="inlineStr">
         <is>
-          <t>コーティング仕様の確定資料（図面・塗装仕様書・補修履歴・膜厚）</t>
+          <t>FRPの樹脂系・積層仕様と補修履歴・膜厚データ</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1165,7 @@
       </c>
       <c r="B25" s="16" t="inlineStr">
         <is>
-          <t>コーティング仕様の食い違い（会議発言FRP／4/1資料エポキシ）の決着を誰に確認するか（操油課図面か機械Grか）</t>
+          <t>4/1調査資料（DEGタンク調査_20260401.pptx）の「エポキシ」記載の訂正を資料所管へ連絡するか</t>
         </is>
       </c>
     </row>

--- a/outputs/T-604_DEG色相_課題分離.xlsx
+++ b/outputs/T-604_DEG色相_課題分離.xlsx
@@ -570,7 +570,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>T-604 DEG色相悪化　課題ツリー（たたき台・合意待ち草案）</t>
+          <t>T-604 DEG色相悪化　課題ツリー（たたき台）</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1140,7 +1140,7 @@
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="13" t="inlineStr">
         <is>
-          <t>合意待ちの点（この草案で確認すること）</t>
+          <t>残る確認点</t>
         </is>
       </c>
       <c r="B23" s="14" t="n"/>
@@ -1153,29 +1153,17 @@
       </c>
       <c r="B24" s="16" t="inlineStr">
         <is>
-          <t>イシューを「全タンク悪化の中でのT-604の速度差＝タンク固有条件の重ね合わせ」と設定し直した向きでよいか</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="37" customHeight="1">
+          <t>4/1調査資料（DEGタンク調査_20260401.pptx）の「エポキシ」記載の訂正を資料所管へ連絡するか</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="26" customHeight="1">
       <c r="A25" s="15" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
       <c r="B25" s="16" t="inlineStr">
-        <is>
-          <t>4/1調査資料（DEGタンク調査_20260401.pptx）の「エポキシ」記載の訂正を資料所管へ連絡するか</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="26" customHeight="1">
-      <c r="A26" s="15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="inlineStr">
         <is>
           <t>「検証方法」列を何に向けた検証として書くか（原因究明用か、会議説明用か）</t>
         </is>
